--- a/supplementary_tables/Supplementary table 2.xlsx
+++ b/supplementary_tables/Supplementary table 2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenshuting/Desktop/drug_toxicity/writing/BIB/BIB_260608/Supplementary data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chenshuting/Desktop/drug_toxicity/writing/BIB/BIB_260610/Supplementary data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1B03FAB-80CF-5340-87AA-D15BA7011F9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EC8F776-8570-AA4B-8D6F-FBA90B327958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="16340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1840" yWindow="580" windowWidth="28800" windowHeight="16340" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Table S2" sheetId="2" r:id="rId1"/>
@@ -215,19 +215,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -243,6 +237,17 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -252,7 +257,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -260,15 +265,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -574,1052 +601,1059 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E62"/>
+  <dimension ref="A1:E63"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>3</v>
-      </c>
+      <c r="A2" s="1"/>
+      <c r="B2" s="1"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="1"/>
+      <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D4" s="2">
         <v>92</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E4" s="2">
         <v>92</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="3" t="s">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="3">
+      <c r="D5" s="2">
         <v>808</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E5" s="2">
         <v>1013</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="3" t="s">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="3">
-        <v>300</v>
-      </c>
-      <c r="E5" s="3">
+      <c r="D6" s="2">
+        <v>300</v>
+      </c>
+      <c r="E6" s="2">
         <v>324</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C7" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="3">
-        <v>300</v>
-      </c>
-      <c r="E6" s="3">
+      <c r="D7" s="2">
+        <v>300</v>
+      </c>
+      <c r="E7" s="2">
         <v>1887</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="3" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="3">
-        <v>300</v>
-      </c>
-      <c r="E7" s="3">
+      <c r="D8" s="2">
+        <v>300</v>
+      </c>
+      <c r="E8" s="2">
         <v>2297</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="3" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C9" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="3">
-        <v>300</v>
-      </c>
-      <c r="E8" s="3">
+      <c r="D9" s="2">
+        <v>300</v>
+      </c>
+      <c r="E9" s="2">
         <v>10710</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="3" t="s">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D9" s="3">
-        <v>300</v>
-      </c>
-      <c r="E9" s="3">
+      <c r="D10" s="2">
+        <v>300</v>
+      </c>
+      <c r="E10" s="2">
         <v>14262</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="3" t="s">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C11" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D10" s="3">
-        <v>300</v>
-      </c>
-      <c r="E10" s="3">
+      <c r="D11" s="2">
+        <v>300</v>
+      </c>
+      <c r="E11" s="2">
         <v>9823</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B11" s="3" t="s">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D11" s="3">
-        <v>300</v>
-      </c>
-      <c r="E11" s="3">
+      <c r="D12" s="2">
+        <v>300</v>
+      </c>
+      <c r="E12" s="2">
         <v>977</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B12" s="3" t="s">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D12" s="3">
-        <v>300</v>
-      </c>
-      <c r="E12" s="3">
+      <c r="D13" s="2">
+        <v>300</v>
+      </c>
+      <c r="E13" s="2">
         <v>7567</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B13" s="3" t="s">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A14" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C14" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="D13" s="3">
-        <v>300</v>
-      </c>
-      <c r="E13" s="3">
+      <c r="D14" s="2">
+        <v>300</v>
+      </c>
+      <c r="E14" s="2">
         <v>10134</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A14" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B14" s="3" t="s">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A15" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="3">
-        <v>300</v>
-      </c>
-      <c r="E14" s="3">
+      <c r="D15" s="2">
+        <v>300</v>
+      </c>
+      <c r="E15" s="2">
         <v>2117</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B15" s="3" t="s">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A16" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C16" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D15" s="3">
-        <v>300</v>
-      </c>
-      <c r="E15" s="3">
+      <c r="D16" s="2">
+        <v>300</v>
+      </c>
+      <c r="E16" s="2">
         <v>882</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A16" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B16" s="3" t="s">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A17" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B17" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="C17" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="D16" s="3">
-        <v>300</v>
-      </c>
-      <c r="E16" s="3">
+      <c r="D17" s="2">
+        <v>300</v>
+      </c>
+      <c r="E17" s="2">
         <v>443</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B17" s="3" t="s">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A18" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B18" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="D17" s="3">
-        <v>300</v>
-      </c>
-      <c r="E17" s="3">
+      <c r="D18" s="2">
+        <v>300</v>
+      </c>
+      <c r="E18" s="2">
         <v>7110</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A18" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B18" s="3" t="s">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A19" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B19" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C19" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D18" s="3">
-        <v>300</v>
-      </c>
-      <c r="E18" s="3">
+      <c r="D19" s="2">
+        <v>300</v>
+      </c>
+      <c r="E19" s="2">
         <v>2287</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A19" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B19" s="3" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B20" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="3">
-        <v>300</v>
-      </c>
-      <c r="E19" s="3">
+      <c r="D20" s="2">
+        <v>300</v>
+      </c>
+      <c r="E20" s="2">
         <v>1744</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A20" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B20" s="3" t="s">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A21" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C21" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D20" s="3">
-        <v>300</v>
-      </c>
-      <c r="E20" s="3">
+      <c r="D21" s="2">
+        <v>300</v>
+      </c>
+      <c r="E21" s="2">
         <v>37050</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A21" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B21" s="3" t="s">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C21" s="3" t="s">
+      <c r="C22" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D21" s="3">
-        <v>300</v>
-      </c>
-      <c r="E21" s="3">
+      <c r="D22" s="2">
+        <v>300</v>
+      </c>
+      <c r="E22" s="2">
         <v>10080</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A22" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B22" s="3" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B23" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="3" t="s">
+      <c r="C23" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D22" s="3">
-        <v>300</v>
-      </c>
-      <c r="E22" s="3">
+      <c r="D23" s="2">
+        <v>300</v>
+      </c>
+      <c r="E23" s="2">
         <v>1675</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A23" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B23" s="3" t="s">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A24" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C23" s="3" t="s">
+      <c r="C24" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D23" s="3">
-        <v>300</v>
-      </c>
-      <c r="E23" s="3">
+      <c r="D24" s="2">
+        <v>300</v>
+      </c>
+      <c r="E24" s="2">
         <v>3417</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A24" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B24" s="3" t="s">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A25" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="C25" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="D24" s="3">
-        <v>300</v>
-      </c>
-      <c r="E24" s="3">
+      <c r="D25" s="2">
+        <v>300</v>
+      </c>
+      <c r="E25" s="2">
         <v>7511</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A25" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B25" s="3" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A26" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C26" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D25" s="3">
-        <v>300</v>
-      </c>
-      <c r="E25" s="3">
+      <c r="D26" s="2">
+        <v>300</v>
+      </c>
+      <c r="E26" s="2">
         <v>2158</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A26" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B26" s="3" t="s">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A27" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B27" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C26" s="3" t="s">
+      <c r="C27" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="D26" s="3">
-        <v>300</v>
-      </c>
-      <c r="E26" s="3">
+      <c r="D27" s="2">
+        <v>300</v>
+      </c>
+      <c r="E27" s="2">
         <v>985</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A27" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B27" s="3" t="s">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A28" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B28" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C27" s="3" t="s">
+      <c r="C28" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D27" s="3">
-        <v>300</v>
-      </c>
-      <c r="E27" s="3">
+      <c r="D28" s="2">
+        <v>300</v>
+      </c>
+      <c r="E28" s="2">
         <v>3772</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A28" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B28" s="3" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A29" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B29" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C28" s="3" t="s">
+      <c r="C29" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D28" s="3">
-        <v>300</v>
-      </c>
-      <c r="E28" s="3">
+      <c r="D29" s="2">
+        <v>300</v>
+      </c>
+      <c r="E29" s="2">
         <v>2646</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A29" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B29" s="3" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C29" s="3" t="s">
+      <c r="C30" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D30" s="2">
         <v>577</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E30" s="2">
         <v>3489</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A30" s="3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B30" s="3" t="s">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C30" s="3" t="s">
+      <c r="C31" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D30" s="3">
+      <c r="D31" s="2">
         <v>323</v>
       </c>
-      <c r="E30" s="3">
+      <c r="E31" s="2">
         <v>323</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A31" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B31" s="3" t="s">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A32" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B32" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C31" s="3" t="s">
+      <c r="C32" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="D31" s="3">
+      <c r="D32" s="2">
         <v>93</v>
       </c>
-      <c r="E31" s="3">
+      <c r="E32" s="2">
         <v>93</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A32" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B32" s="3" t="s">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A33" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B33" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C32" s="3" t="s">
+      <c r="C33" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="3">
+      <c r="D33" s="2">
         <v>403</v>
       </c>
-      <c r="E32" s="3">
+      <c r="E33" s="2">
         <v>2909</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A33" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B33" s="3" t="s">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A34" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B34" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="C34" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="D33" s="3">
+      <c r="D34" s="2">
         <v>404</v>
       </c>
-      <c r="E33" s="3">
+      <c r="E34" s="2">
         <v>7108</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A34" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B34" s="3" t="s">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B35" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C34" s="3" t="s">
+      <c r="C35" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D34" s="3">
-        <v>300</v>
-      </c>
-      <c r="E34" s="3">
+      <c r="D35" s="2">
+        <v>300</v>
+      </c>
+      <c r="E35" s="2">
         <v>25926</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A35" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B35" s="3" t="s">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B36" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C35" s="3" t="s">
+      <c r="C36" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D35" s="3">
-        <v>300</v>
-      </c>
-      <c r="E35" s="3">
+      <c r="D36" s="2">
+        <v>300</v>
+      </c>
+      <c r="E36" s="2">
         <v>5559</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A36" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B36" s="3" t="s">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B37" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C36" s="3" t="s">
+      <c r="C37" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="D36" s="3">
-        <v>300</v>
-      </c>
-      <c r="E36" s="3">
+      <c r="D37" s="2">
+        <v>300</v>
+      </c>
+      <c r="E37" s="2">
         <v>9096</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A37" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B37" s="3" t="s">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B38" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C37" s="3" t="s">
+      <c r="C38" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D37" s="3">
-        <v>300</v>
-      </c>
-      <c r="E37" s="3">
+      <c r="D38" s="2">
+        <v>300</v>
+      </c>
+      <c r="E38" s="2">
         <v>1771</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A38" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B38" s="3" t="s">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B39" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C38" s="3" t="s">
+      <c r="C39" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="3">
-        <v>300</v>
-      </c>
-      <c r="E38" s="3">
+      <c r="D39" s="2">
+        <v>300</v>
+      </c>
+      <c r="E39" s="2">
         <v>767</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B39" s="3" t="s">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C39" s="3" t="s">
+      <c r="C40" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D39" s="3">
-        <v>300</v>
-      </c>
-      <c r="E39" s="3">
+      <c r="D40" s="2">
+        <v>300</v>
+      </c>
+      <c r="E40" s="2">
         <v>1188</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B40" s="3" t="s">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A41" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C40" s="3" t="s">
+      <c r="C41" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="D40" s="3">
-        <v>300</v>
-      </c>
-      <c r="E40" s="3">
+      <c r="D41" s="2">
+        <v>300</v>
+      </c>
+      <c r="E41" s="2">
         <v>18710</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B41" s="3" t="s">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B42" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C41" s="3" t="s">
+      <c r="C42" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="D41" s="3">
-        <v>300</v>
-      </c>
-      <c r="E41" s="3">
+      <c r="D42" s="2">
+        <v>300</v>
+      </c>
+      <c r="E42" s="2">
         <v>19891</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A42" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B42" s="3" t="s">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B43" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="C42" s="3" t="s">
+      <c r="C43" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D42" s="3">
-        <v>300</v>
-      </c>
-      <c r="E42" s="3">
+      <c r="D43" s="2">
+        <v>300</v>
+      </c>
+      <c r="E43" s="2">
         <v>2042</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A43" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B43" s="3" t="s">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A44" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B44" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C43" s="3" t="s">
+      <c r="C44" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="D43" s="3">
-        <v>300</v>
-      </c>
-      <c r="E43" s="3">
+      <c r="D44" s="2">
+        <v>300</v>
+      </c>
+      <c r="E44" s="2">
         <v>10462</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A44" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B44" s="3" t="s">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A45" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B45" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="C45" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D44" s="3">
-        <v>300</v>
-      </c>
-      <c r="E44" s="3">
+      <c r="D45" s="2">
+        <v>300</v>
+      </c>
+      <c r="E45" s="2">
         <v>6100</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B45" s="3" t="s">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A46" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C45" s="3" t="s">
+      <c r="C46" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D45" s="3">
-        <v>300</v>
-      </c>
-      <c r="E45" s="3">
+      <c r="D46" s="2">
+        <v>300</v>
+      </c>
+      <c r="E46" s="2">
         <v>14396</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A46" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B46" s="3" t="s">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A47" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B47" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C46" s="3" t="s">
+      <c r="C47" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="D46" s="3">
-        <v>300</v>
-      </c>
-      <c r="E46" s="3">
+      <c r="D47" s="2">
+        <v>300</v>
+      </c>
+      <c r="E47" s="2">
         <v>550</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A47" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B47" s="3" t="s">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A48" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B48" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C47" s="3" t="s">
+      <c r="C48" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="D47" s="3">
-        <v>300</v>
-      </c>
-      <c r="E47" s="3">
+      <c r="D48" s="2">
+        <v>300</v>
+      </c>
+      <c r="E48" s="2">
         <v>611</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A48" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B48" s="3" t="s">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B49" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C48" s="3" t="s">
+      <c r="C49" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="D48" s="3">
-        <v>300</v>
-      </c>
-      <c r="E48" s="3">
+      <c r="D49" s="2">
+        <v>300</v>
+      </c>
+      <c r="E49" s="2">
         <v>5804</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A49" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49" s="3" t="s">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B50" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C49" s="3" t="s">
+      <c r="C50" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="D49" s="3">
-        <v>300</v>
-      </c>
-      <c r="E49" s="3">
+      <c r="D50" s="2">
+        <v>300</v>
+      </c>
+      <c r="E50" s="2">
         <v>3956</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A50" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="3" t="s">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A51" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B51" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C50" s="3" t="s">
+      <c r="C51" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D50" s="3">
-        <v>300</v>
-      </c>
-      <c r="E50" s="3">
+      <c r="D51" s="2">
+        <v>300</v>
+      </c>
+      <c r="E51" s="2">
         <v>1103</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A51" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B51" s="3" t="s">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A52" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B52" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C51" s="3" t="s">
+      <c r="C52" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="D51" s="3">
-        <v>300</v>
-      </c>
-      <c r="E51" s="3">
+      <c r="D52" s="2">
+        <v>300</v>
+      </c>
+      <c r="E52" s="2">
         <v>409</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A52" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B52" s="3" t="s">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A53" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C52" s="3" t="s">
+      <c r="C53" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D52" s="3">
-        <v>300</v>
-      </c>
-      <c r="E52" s="3">
+      <c r="D53" s="2">
+        <v>300</v>
+      </c>
+      <c r="E53" s="2">
         <v>5778</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A53" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B53" s="3" t="s">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A54" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B54" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C53" s="3" t="s">
+      <c r="C54" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="D53" s="3">
-        <v>300</v>
-      </c>
-      <c r="E53" s="3">
+      <c r="D54" s="2">
+        <v>300</v>
+      </c>
+      <c r="E54" s="2">
         <v>767</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A54" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B54" s="3" t="s">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B55" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C54" s="3" t="s">
+      <c r="C55" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="D54" s="3">
-        <v>300</v>
-      </c>
-      <c r="E54" s="3">
+      <c r="D55" s="2">
+        <v>300</v>
+      </c>
+      <c r="E55" s="2">
         <v>1034</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A55" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B55" s="3" t="s">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A56" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B56" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C55" s="3" t="s">
+      <c r="C56" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D55" s="3">
+      <c r="D56" s="2">
         <v>269</v>
       </c>
-      <c r="E55" s="3">
+      <c r="E56" s="2">
         <v>269</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A56" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B56" s="3" t="s">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A57" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="B57" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C56" s="3" t="s">
+      <c r="C57" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="D56" s="3">
+      <c r="D57" s="2">
         <v>631</v>
       </c>
-      <c r="E56" s="3">
+      <c r="E57" s="2">
         <v>4367</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A57" s="3" t="s">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A58" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B57" s="3" t="s">
+      <c r="B58" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C57" s="3" t="s">
+      <c r="C58" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="D57" s="3">
-        <v>300</v>
-      </c>
-      <c r="E57" s="3">
+      <c r="D58" s="2">
+        <v>300</v>
+      </c>
+      <c r="E58" s="2">
         <v>3873</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A58" s="3" t="s">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A59" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="B59" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C58" s="3" t="s">
+      <c r="C59" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D58" s="3">
-        <v>300</v>
-      </c>
-      <c r="E58" s="3">
+      <c r="D59" s="2">
+        <v>300</v>
+      </c>
+      <c r="E59" s="2">
         <v>3741</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A59" s="3" t="s">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A60" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B59" s="3" t="s">
+      <c r="B60" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C59" s="3" t="s">
+      <c r="C60" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D59" s="3">
-        <v>300</v>
-      </c>
-      <c r="E59" s="3">
+      <c r="D60" s="2">
+        <v>300</v>
+      </c>
+      <c r="E60" s="2">
         <v>3202</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A60" s="3" t="s">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B60" s="3" t="s">
+      <c r="B61" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C60" s="3" t="s">
+      <c r="C61" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D60" s="3">
-        <v>300</v>
-      </c>
-      <c r="E60" s="3">
+      <c r="D61" s="2">
+        <v>300</v>
+      </c>
+      <c r="E61" s="2">
         <v>12909</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A61" s="3" t="s">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="B61" s="3" t="s">
+      <c r="B62" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C61" s="3" t="s">
+      <c r="C62" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="D61" s="3">
-        <v>300</v>
-      </c>
-      <c r="E61" s="3">
+      <c r="D62" s="2">
+        <v>300</v>
+      </c>
+      <c r="E62" s="2">
         <v>7265</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A62" s="3" t="s">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A63" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="B62" s="3" t="s">
+      <c r="B63" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="C62" s="3" t="s">
+      <c r="C63" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D62" s="3">
-        <v>300</v>
-      </c>
-      <c r="E62" s="3">
+      <c r="D63" s="5">
+        <v>300</v>
+      </c>
+      <c r="E63" s="5">
         <v>16986</v>
       </c>
     </row>
